--- a/data/may/WOMEN GYM5 TIME SHEET MAY 2026.xlsx
+++ b/data/may/WOMEN GYM5 TIME SHEET MAY 2026.xlsx
@@ -1,32 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Makkah Yard\HR\TIME SHEET\TIME SHEET 2026\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BB3B4C4-261F-4E4F-BBDA-8880753EE009}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="11520" windowHeight="10440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -45,12 +41,12 @@
     <t>الحاله</t>
   </si>
   <si>
+    <t>صفاء الرفاعي</t>
+  </si>
+  <si>
     <t>غياب بدون سكليف</t>
   </si>
   <si>
-    <t>صفاء الرفاعي</t>
-  </si>
-  <si>
     <t>استئذان</t>
   </si>
   <si>
@@ -72,12 +68,15 @@
     <t xml:space="preserve">اسراء </t>
   </si>
   <si>
+    <t>من 16 الى 24 /5/2026</t>
+  </si>
+  <si>
+    <t>غياب بسكليف</t>
+  </si>
+  <si>
     <t>نهى مجلد</t>
   </si>
   <si>
-    <t>غياب بسكليف</t>
-  </si>
-  <si>
     <t>17-19-21-24/5/2026</t>
   </si>
   <si>
@@ -87,28 +86,25 @@
     <t>رانيه</t>
   </si>
   <si>
+    <t>من 18 الى 24 /5/2026</t>
+  </si>
+  <si>
+    <t>شيماء بدوي</t>
+  </si>
+  <si>
     <t>23-24/5/2026</t>
   </si>
   <si>
+    <t>23-24/05/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">هبه </t>
   </si>
   <si>
     <t>الاء رباح</t>
   </si>
   <si>
-    <t>23-24/05/2026</t>
-  </si>
-  <si>
-    <t>من 18 الى 24 /5/2026</t>
-  </si>
-  <si>
-    <t>من 16 الى 24 /5/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">فردوس </t>
-  </si>
-  <si>
-    <t>شيماء بدوي</t>
   </si>
   <si>
     <t xml:space="preserve">ايمان </t>
@@ -117,22 +113,180 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Sakkal Majalla"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -141,13 +295,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.349986266670736"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -157,8 +323,200 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -168,61 +526,362 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="58" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="58" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -271,7 +930,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -306,7 +965,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -480,27 +1139,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C73"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="21.75" x14ac:dyDescent="0.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D73"/>
+  <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="21.6" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="16" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="24.712962962963" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.287037037037" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9.13888888888889" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,20 +1165,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A2" s="2" t="s">
+    <row r="2" hidden="1" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4">
+        <v>46145</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3">
-        <v>46145</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="3" hidden="1" spans="1:4">
+      <c r="A3" s="5" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A3" s="5" t="s">
-        <v>4</v>
       </c>
       <c r="B3" s="6">
         <v>46147</v>
@@ -533,86 +1187,87 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A4" s="5" t="s">
+    <row r="4" hidden="1" spans="1:4">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <v>46148</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A5" s="5" t="s">
+    <row r="5" hidden="1" spans="1:4">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>46149</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A6" s="5" t="s">
+    <row r="6" hidden="1" spans="1:4">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>46149</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A7" s="2" t="s">
+    <row r="7" hidden="1" spans="1:4">
+      <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="8">
         <v>46151</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" hidden="1" spans="1:4">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4">
+        <v>46151</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" hidden="1" spans="1:4">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4">
+        <v>46156</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" hidden="1" spans="1:4">
+      <c r="A10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" hidden="1" spans="1:4">
+      <c r="A11" s="5" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3">
-        <v>46151</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46156</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A11" s="5" t="s">
-        <v>4</v>
       </c>
       <c r="B11" s="6">
         <v>46158</v>
@@ -621,294 +1276,303 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="6">
+    <row r="12" hidden="1" spans="1:4">
+      <c r="A12" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12">
         <v>46158</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A13" s="5" t="s">
+    <row r="13" hidden="1" spans="1:4">
+      <c r="A13" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A14" s="5" t="s">
+      <c r="C13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="6" t="s">
+    </row>
+    <row r="14" hidden="1" spans="1:4">
+      <c r="A14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" hidden="1" spans="1:4">
+      <c r="A16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A16" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="6">
+    <row r="17" hidden="1" spans="1:4">
+      <c r="A17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="12">
         <v>46158</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A18" s="2" t="s">
+    <row r="18" hidden="1" spans="1:4">
+      <c r="A18" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" hidden="1" spans="1:4">
+      <c r="A19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="4">
+        <v>46166</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="3">
-        <v>46161</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="6">
-        <v>46166</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="B20" s="12">
+        <v>46163</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A20" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="6">
-        <v>46163</v>
-      </c>
-      <c r="C20" s="5" t="s">
+    <row r="21" hidden="1" spans="1:4">
+      <c r="A21" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="12">
+        <v>46172</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="12">
+        <v>46173</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A21" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="6">
-        <v>46172</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A22" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="6">
-        <v>46173</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="5"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="5"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="5"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="5"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="5"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="5"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="B30" s="8"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="B31" s="8"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="B32" s="8"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B33" s="8"/>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B34" s="8"/>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B35" s="8"/>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B36" s="8"/>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B37" s="8"/>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B38" s="8"/>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B39" s="8"/>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B40" s="8"/>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B41" s="8"/>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B42" s="8"/>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B43" s="8"/>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B44" s="8"/>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B45" s="8"/>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B46" s="8"/>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B47" s="8"/>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B48" s="8"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B49" s="8"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B50" s="8"/>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B51" s="8"/>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B52" s="8"/>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B53" s="8"/>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B54" s="8"/>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B55" s="8"/>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B56" s="8"/>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B57" s="8"/>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B58" s="8"/>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B59" s="8"/>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B60" s="8"/>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B61" s="8"/>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B62" s="8"/>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B63" s="8"/>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B64" s="8"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B65" s="8"/>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B66" s="8"/>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B67" s="8"/>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B68" s="8"/>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B70" s="8"/>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B71" s="8"/>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B72" s="8"/>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.5">
-      <c r="B73" s="8"/>
+    <row r="23" spans="1:4">
+      <c r="A23" s="11"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="11"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="11"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="11"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="11"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="11"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="11"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="11"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="11"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="11"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="11"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="11"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="B30" s="13"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="B31" s="13"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="B32" s="13"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="13"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="13"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="13"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="13"/>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="13"/>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="13"/>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="13"/>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="13"/>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="13"/>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="13"/>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="13"/>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="13"/>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="13"/>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="13"/>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="13"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="13"/>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="13"/>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="13"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="13"/>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="13"/>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="13"/>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="13"/>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="13"/>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="13"/>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="13"/>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="13"/>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="13"/>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="13"/>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="13"/>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="13"/>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="13"/>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="13"/>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="13"/>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="13"/>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="13"/>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="13"/>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="13"/>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="13"/>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="13"/>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:C22" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="شيماء بدوي"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>